--- a/public/documents/pieces-reponse-1/R1-tickets-a-zero.xlsx
+++ b/public/documents/pieces-reponse-1/R1-tickets-a-zero.xlsx
@@ -80,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -88,6 +88,12 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -102387,13 +102393,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -102403,6 +102413,13 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Les trois sont expliques un a un, et l'explication est relue dans l'annexe C : numero de cloture Z, nombre de lignes d'articles, libelles. Deux sont des repas integralement offerts, dont toutes les lignes sont a 0,00 € ; le troisieme ne porte aucune ligne au detail des tickets.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -102424,65 +102441,129 @@
           <t>N° de ticket</t>
         </is>
       </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Cloture Z</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Lignes au detail (annexe C)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Articles</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Explication</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2022-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2022-2023</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>2022-04-29</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>13:15</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="5" t="n">
         <v>15</v>
       </c>
+      <c r="E5" s="5" t="n">
+        <v>2950</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Martini Blanc, Schweppes, Luna, Complète, Salade Verte aux Noi, POMMES FRITES, FONDUE VIN JAUNE</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Repas integralement offert. Le ticket porte 7 lignes d'articles, toutes au prix de 0,00 € dans l'annexe C : rien n'a ete encaisse, donc rien n'a ete efface. Le detail est reproduit ligne a ligne a la page « Articles a prix 0 € ».</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2022-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2022-2023</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>2022-12-28</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>20:05</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="5" t="n">
         <v>17</v>
       </c>
+      <c r="E6" s="5" t="n">
+        <v>3123</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Chat perché, Père Gregoire, Luna, Menu 'Galette', DADOULET, LOURNETTE</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Repas integralement offert. Le ticket porte 6 lignes d'articles, toutes au prix de 0,00 € dans l'annexe C : rien n'a ete encaisse, donc rien n'a ete efface. Le detail est reproduit ligne a ligne a la page « Articles a prix 0 € ».</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2022-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2022-2023</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>2023-03-23</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>20:18</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="5" t="n">
         <v>5</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>3152</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Aucune ligne dans le detail des tickets (annexe C) : table ouverte puis refermee sans commande. La journee n'y porte que les tickets n° 1 a n° 4 (cloture Z n° 3152).</t>
+        </is>
       </c>
     </row>
   </sheetData>
